--- a/data/trans_orig/P43E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P43E-Habitat-trans_orig.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -525,25 +525,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha citología vaginal en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última citología vaginal en 2012 (tasa de respuesta: 98,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +547,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -563,17 +556,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -644,41 +626,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -701,13 +648,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -722,37 +662,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71583</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56792</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55912</t>
+          <t>56792</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88363</t>
+          <t>89436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>71583</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>55912</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>88363</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>16,73%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>13,07%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>20,65%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -835,37 +740,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>330</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>356329</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>338476</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>371120</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339549</t>
+          <t>338476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>372000</t>
+          <t>371120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>356329</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>339549</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>372000</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>83,27%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>79,35%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>86,93%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -948,37 +818,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>427912</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>427912</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>427912</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1012,41 +882,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>427912</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>427912</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>427912</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1065,37 +900,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>161991</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139172</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>185545</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138271</t>
+          <t>139172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>185094</t>
+          <t>185545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,47 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>161991</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>138271</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>185094</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>24,79%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>21,16%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -1178,37 +978,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>447</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>491381</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>467827</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>514200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>468278</t>
+          <t>467827</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>515101</t>
+          <t>514200</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,47 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>491381</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>468278</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>515101</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>75,21%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>71,67%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>78,84%</t>
+          <t>78,7%</t>
         </is>
       </c>
     </row>
@@ -1291,37 +1056,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>591</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>653372</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>653372</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>653372</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1355,41 +1120,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>653372</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>653372</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>653372</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1408,37 +1138,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131691</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111283</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111752</t>
+          <t>111283</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155419</t>
+          <t>155195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,47 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>131691</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>111752</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>155419</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>25,12%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>21,32%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>29,65%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -1521,37 +1216,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>360</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>392529</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>369025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412937</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>368801</t>
+          <t>369025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>412468</t>
+          <t>412937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,47 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>392529</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>368801</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>412468</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>74,88%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>70,35%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>78,68%</t>
+          <t>78,77%</t>
         </is>
       </c>
     </row>
@@ -1634,37 +1294,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>524220</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>524220</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>524220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1698,41 +1358,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>524220</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>524220</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>524220</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1751,37 +1376,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152151</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129951</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>174041</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131137</t>
+          <t>129951</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176695</t>
+          <t>174041</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,47 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>152151</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>131137</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>176695</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>20,38%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>27,46%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -1864,37 +1454,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>469</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>491370</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>469480</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>513570</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>466826</t>
+          <t>469480</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>512384</t>
+          <t>513570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,47 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>491370</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>466826</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>512384</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>76,36%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>72,54%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>79,62%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -1977,37 +1532,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>643521</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>643521</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>643521</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2041,41 +1596,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>643521</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>643521</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>643521</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2094,37 +1614,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>461</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>517415</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>474104</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>558644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +1659,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>477118</t>
+          <t>474104</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>563259</t>
+          <t>558644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,47 +1674,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>517415</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>477118</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>563259</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>23,01%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>21,21%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>25,04%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -2207,37 +1692,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1731610</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1690381</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1774921</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +1737,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1685766</t>
+          <t>1690381</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1771907</t>
+          <t>1774921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,47 +1752,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1606</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1731610</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1685766</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1771907</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>76,99%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>74,96%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>78,79%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -2320,37 +1770,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2249025</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2249025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2249025</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2384,41 +1834,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2249025</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>2249025</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2249025</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2432,14 +1847,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2453,7 +1867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2472,25 +1886,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha citología vaginal en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última citología vaginal en 2016 (tasa de respuesta: 96,09%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +1908,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2510,17 +1917,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2591,41 +1987,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2648,13 +2009,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2669,37 +2023,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40255</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29475</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54976</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2068,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28437</t>
+          <t>29475</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53182</t>
+          <t>54976</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,47 +2083,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>40255</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>28437</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>53182</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -2782,37 +2101,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>309</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308536</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>293815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>319316</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2146,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295609</t>
+          <t>293815</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>320354</t>
+          <t>319316</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,47 +2161,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>308536</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>295609</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>320354</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>88,46%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>84,75%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -2895,37 +2179,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>348</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>348791</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>348791</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>348791</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2959,41 +2243,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>348791</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>348791</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>348791</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3012,37 +2261,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96417</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78866</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +2306,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80493</t>
+          <t>78866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118874</t>
+          <t>115825</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,47 +2321,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>96417</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>80493</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>118874</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -3125,37 +2339,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>504</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>534894</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>515486</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>552445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +2384,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512437</t>
+          <t>515486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>550818</t>
+          <t>552445</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,47 +2399,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>534894</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>512437</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>550818</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>84,73%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>81,17%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>87,25%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -3238,37 +2417,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>596</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>631311</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>631311</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>631311</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3302,41 +2481,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>631311</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>631311</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>631311</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3355,37 +2499,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>87647</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106171</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +2544,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69270</t>
+          <t>72059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>106171</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,47 +2559,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>87647</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>69270</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>104150</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>17,73%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>14,01%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>21,07%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -3468,37 +2577,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>384</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>406718</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>388194</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>422306</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +2622,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>390215</t>
+          <t>388194</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425095</t>
+          <t>422306</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,47 +2637,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>406718</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>390215</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>425095</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>82,27%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>78,93%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>85,99%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -3581,37 +2655,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>468</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>494365</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>494365</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>494365</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3645,41 +2719,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>494365</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>494365</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>494365</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3698,37 +2737,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>128720</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106878</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>150533</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +2782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108351</t>
+          <t>106878</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150163</t>
+          <t>150533</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,47 +2797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>128720</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>108351</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>150163</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>15,95%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -3811,37 +2815,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>514</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>550488</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>528675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>572330</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +2860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>529045</t>
+          <t>528675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>570857</t>
+          <t>572330</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,47 +2875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>550488</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>529045</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>570857</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>81,05%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>77,89%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>84,05%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -3924,37 +2893,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>628</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>679208</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>679208</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>679208</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3988,41 +2957,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>679208</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>679208</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>679208</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4041,37 +2975,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>329</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353039</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>319342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>387366</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +3020,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>321040</t>
+          <t>319342</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>390812</t>
+          <t>387366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,47 +3035,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>353039</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>321040</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>390812</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>16,39%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -4154,37 +3053,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1800635</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1766308</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1834332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +3098,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1762862</t>
+          <t>1766308</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1832634</t>
+          <t>1834332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,47 +3113,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1800635</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1762862</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1832634</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>83,61%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>85,09%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -4267,37 +3131,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2153674</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2153674</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2153674</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4331,41 +3195,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2153674</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>2153674</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2153674</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4379,14 +3208,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -4400,7 +3228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4419,25 +3247,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha citología vaginal en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última citología vaginal en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +3269,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4457,17 +3278,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -4538,41 +3348,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -4595,13 +3370,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4616,37 +3384,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35712</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +3429,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27399</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45536</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,47 +3444,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>35712</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>27399</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>45536</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>10,25%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>17,03%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -4729,37 +3462,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>436</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>231721</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>221950</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>239583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +3507,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221897</t>
+          <t>221950</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>240034</t>
+          <t>239583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,47 +3522,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>231721</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>221897</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>240034</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>86,65%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>82,97%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>89,75%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -4842,37 +3540,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267433</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267433</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4906,41 +3604,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>267433</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>267433</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>267433</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4959,37 +3622,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79033</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67308</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92283</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +3667,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67075</t>
+          <t>67308</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90782</t>
+          <t>92283</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,47 +3682,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>79033</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>67075</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>90782</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>20,77%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>17,63%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>23,86%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -5072,37 +3700,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>513</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301395</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288145</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>313120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +3745,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289646</t>
+          <t>288145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313353</t>
+          <t>313120</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,47 +3760,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>301395</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>289646</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>313353</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>79,23%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>76,14%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>82,37%</t>
+          <t>82,31%</t>
         </is>
       </c>
     </row>
@@ -5185,37 +3778,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>380428</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>380428</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>380428</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5249,41 +3842,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>380428</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>380428</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>380428</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5302,37 +3860,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>149</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104131</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70305</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>122105</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +3905,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72378</t>
+          <t>70305</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123008</t>
+          <t>122105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,47 +3920,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>104131</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>72378</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>123008</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>29,42%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>20,45%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>34,75%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -5415,37 +3938,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>351</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>249805</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>231831</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +3983,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>230928</t>
+          <t>231831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>281558</t>
+          <t>283631</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,47 +3998,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>249805</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>230928</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>281558</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>70,58%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>65,25%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>79,55%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -5528,37 +4016,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353936</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353936</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353936</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5592,41 +4080,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>353936</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>353936</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>353936</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5645,37 +4098,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>219</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141134</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>168453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +4143,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89601</t>
+          <t>96337</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169168</t>
+          <t>168453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,47 +4158,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>141134</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>89601</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>169168</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>24,81%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>15,75%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>29,73%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -5758,37 +4176,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>558</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>427821</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>400502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>472618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +4221,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>399787</t>
+          <t>400502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>479354</t>
+          <t>472618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,47 +4236,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>427821</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>399787</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>479354</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>75,19%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>70,27%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>84,25%</t>
+          <t>83,07%</t>
         </is>
       </c>
     </row>
@@ -5871,37 +4254,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>777</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568955</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568955</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5935,41 +4318,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>568955</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>568955</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>568955</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5988,37 +4336,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>560</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>360010</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301053</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>395733</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +4381,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>301917</t>
+          <t>301053</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>392688</t>
+          <t>395733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,47 +4396,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>360010</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>301917</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>392688</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>22,92%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -6101,37 +4414,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1210742</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1175019</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1269699</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +4459,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1178064</t>
+          <t>1175019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1268835</t>
+          <t>1269699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,47 +4474,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1858</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1210742</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1178064</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1268835</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>77,08%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>80,78%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -6214,37 +4492,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1570752</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1570752</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1570752</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6278,41 +4556,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2418</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1570752</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>1570752</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>1570752</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6326,14 +4569,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P43E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P43E-Habitat-trans_orig.xlsx
@@ -672,12 +672,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56792</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89436</t>
+          <t>89742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56792</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89436</t>
+          <t>89742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>338476</t>
+          <t>338170</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>371120</t>
+          <t>370005</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>338476</t>
+          <t>338170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>371120</t>
+          <t>370005</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139172</t>
+          <t>138825</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>185545</t>
+          <t>185793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>139172</t>
+          <t>138825</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>185545</t>
+          <t>185793</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467827</t>
+          <t>467579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514200</t>
+          <t>514547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>467827</t>
+          <t>467579</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514200</t>
+          <t>514547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,75%</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111283</t>
+          <t>110211</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155195</t>
+          <t>155377</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111283</t>
+          <t>110211</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155195</t>
+          <t>155377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>369025</t>
+          <t>368843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>412937</t>
+          <t>414009</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>369025</t>
+          <t>368843</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>412937</t>
+          <t>414009</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,98%</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129951</t>
+          <t>129789</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174041</t>
+          <t>175778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129951</t>
+          <t>129789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>174041</t>
+          <t>175778</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>469480</t>
+          <t>467743</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>513570</t>
+          <t>513732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>469480</t>
+          <t>467743</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>513570</t>
+          <t>513732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,83%</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>474104</t>
+          <t>478474</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>558644</t>
+          <t>559306</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>474104</t>
+          <t>478474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>558644</t>
+          <t>559306</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1690381</t>
+          <t>1689719</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1774921</t>
+          <t>1770551</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1690381</t>
+          <t>1689719</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1774921</t>
+          <t>1770551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29475</t>
+          <t>29360</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54976</t>
+          <t>53302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29475</t>
+          <t>29360</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54976</t>
+          <t>53302</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>293815</t>
+          <t>295489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>319316</t>
+          <t>319431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293815</t>
+          <t>295489</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>319316</t>
+          <t>319431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78866</t>
+          <t>78749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115825</t>
+          <t>114452</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78866</t>
+          <t>78749</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115825</t>
+          <t>114452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>515486</t>
+          <t>516859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>552445</t>
+          <t>552562</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>515486</t>
+          <t>516859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>552445</t>
+          <t>552562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72059</t>
+          <t>70413</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106171</t>
+          <t>105437</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72059</t>
+          <t>70413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106171</t>
+          <t>105437</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2587,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>388194</t>
+          <t>388928</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422306</t>
+          <t>423952</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>388194</t>
+          <t>388928</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>422306</t>
+          <t>423952</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -2747,12 +2747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106878</t>
+          <t>108634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150533</t>
+          <t>151436</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2782,12 +2782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106878</t>
+          <t>108634</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150533</t>
+          <t>151436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -2825,12 +2825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>528675</t>
+          <t>527772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>572330</t>
+          <t>570574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>528675</t>
+          <t>527772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>572330</t>
+          <t>570574</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,01%</t>
         </is>
       </c>
     </row>
@@ -2985,12 +2985,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>319342</t>
+          <t>318740</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>387366</t>
+          <t>387912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>319342</t>
+          <t>318740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>387366</t>
+          <t>387912</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1766308</t>
+          <t>1765762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1834332</t>
+          <t>1834934</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1766308</t>
+          <t>1765762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1834332</t>
+          <t>1834934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -3389,32 +3389,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35712</t>
+          <t>37638</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>48191</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3424,32 +3424,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35712</t>
+          <t>37638</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>48191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -3467,32 +3467,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>231721</t>
+          <t>247799</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221950</t>
+          <t>237246</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239583</t>
+          <t>256004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3502,32 +3502,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>231721</t>
+          <t>247799</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221950</t>
+          <t>237246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239583</t>
+          <t>256004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -3545,17 +3545,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>267433</t>
+          <t>285437</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>267433</t>
+          <t>285437</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>267433</t>
+          <t>285437</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3580,17 +3580,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>267433</t>
+          <t>285437</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>267433</t>
+          <t>285437</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>267433</t>
+          <t>285437</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3627,32 +3627,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79033</t>
+          <t>89468</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67308</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92283</t>
+          <t>104497</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3662,32 +3662,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79033</t>
+          <t>89468</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67308</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92283</t>
+          <t>104497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -3705,32 +3705,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>301395</t>
+          <t>333049</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>288145</t>
+          <t>318020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>313120</t>
+          <t>347669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3740,32 +3740,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>301395</t>
+          <t>333049</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288145</t>
+          <t>318020</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313120</t>
+          <t>347669</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -3783,17 +3783,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>380428</t>
+          <t>422517</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>380428</t>
+          <t>422517</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>380428</t>
+          <t>422517</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3818,17 +3818,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>380428</t>
+          <t>422517</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>380428</t>
+          <t>422517</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380428</t>
+          <t>422517</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3865,32 +3865,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>104131</t>
+          <t>115376</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70305</t>
+          <t>100698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122105</t>
+          <t>133047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3900,32 +3900,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>104131</t>
+          <t>115376</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70305</t>
+          <t>100698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122105</t>
+          <t>133047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -3943,32 +3943,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>249805</t>
+          <t>254187</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>231831</t>
+          <t>236516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283631</t>
+          <t>268865</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3978,32 +3978,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>249805</t>
+          <t>254187</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>231831</t>
+          <t>236516</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>283631</t>
+          <t>268865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -4021,17 +4021,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>353936</t>
+          <t>369563</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>353936</t>
+          <t>369563</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>353936</t>
+          <t>369563</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>353936</t>
+          <t>369563</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>353936</t>
+          <t>369563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>353936</t>
+          <t>369563</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4103,32 +4103,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>141134</t>
+          <t>152723</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96337</t>
+          <t>135411</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168453</t>
+          <t>169968</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4138,32 +4138,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>141134</t>
+          <t>152723</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96337</t>
+          <t>135411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168453</t>
+          <t>169968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -4181,32 +4181,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>427821</t>
+          <t>379273</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>400502</t>
+          <t>362028</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>472618</t>
+          <t>396585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4216,32 +4216,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>427821</t>
+          <t>379273</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>400502</t>
+          <t>362028</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>472618</t>
+          <t>396585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -4259,17 +4259,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>568955</t>
+          <t>531996</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>568955</t>
+          <t>531996</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>568955</t>
+          <t>531996</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4294,17 +4294,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>568955</t>
+          <t>531996</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>568955</t>
+          <t>531996</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>568955</t>
+          <t>531996</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4341,32 +4341,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>360010</t>
+          <t>395204</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>301053</t>
+          <t>365309</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>395733</t>
+          <t>424889</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4376,32 +4376,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>360010</t>
+          <t>395204</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>301053</t>
+          <t>365309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>395733</t>
+          <t>424889</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -4419,32 +4419,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1210742</t>
+          <t>1214309</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1175019</t>
+          <t>1184624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1269699</t>
+          <t>1244204</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4454,32 +4454,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1210742</t>
+          <t>1214309</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1175019</t>
+          <t>1184624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1269699</t>
+          <t>1244204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -4497,17 +4497,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1609513</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1609513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1609513</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1609513</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1609513</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1570752</t>
+          <t>1609513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
